--- a/artfynd/A 40231-2023 artfynd.xlsx
+++ b/artfynd/A 40231-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113028442</v>
       </c>
       <c r="B2" t="n">
-        <v>91313</v>
+        <v>91329</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -778,10 +778,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113027943</v>
+        <v>113028682</v>
       </c>
       <c r="B3" t="n">
-        <v>97298</v>
+        <v>99570</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,37 +790,28 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550432</v>
+        <v>550249</v>
       </c>
       <c r="R3" t="n">
-        <v>6583787</v>
+        <v>6583954</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,10 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113028682</v>
+        <v>113027943</v>
       </c>
       <c r="B4" t="n">
-        <v>99554</v>
+        <v>97314</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -902,28 +893,37 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550249</v>
+        <v>550432</v>
       </c>
       <c r="R4" t="n">
-        <v>6583954</v>
+        <v>6583787</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 40231-2023 artfynd.xlsx
+++ b/artfynd/A 40231-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
